--- a/MachineMonitor.xlsx
+++ b/MachineMonitor.xlsx
@@ -18,6 +18,13 @@
     <definedName name="EndDate">Dashboard!$C$8</definedName>
     <definedName name="TagFilter">Dashboard!$G$7</definedName>
     <definedName name="MetricFocus">Dashboard!$G$8</definedName>
+    <definedName name="AddMID">Dashboard!$B$16</definedName>
+    <definedName name="AddName">Dashboard!$D$16</definedName>
+    <definedName name="AddTag">Dashboard!$F$16</definedName>
+    <definedName name="AddM1">Dashboard!$H$16</definedName>
+    <definedName name="AddM2">Dashboard!$J$16</definedName>
+    <definedName name="AddM3">Dashboard!$L$16</definedName>
+    <definedName name="LastTag">Dashboard!$AH$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +37,7 @@
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +70,11 @@
     </font>
     <font>
       <name val="Consolas"/>
+      <color rgb="000F1A20"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
       <color rgb="006E8A96"/>
       <sz val="9"/>
     </font>
@@ -78,8 +90,14 @@
       <color rgb="00E6EEF1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="000F1A20"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -103,11 +121,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFDF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8A33D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F3E4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -131,6 +159,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C87A1F"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C87A1F"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C87A1F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C87A1F"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="00C87A1F"/>
       </left>
@@ -145,7 +187,7 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -162,20 +204,32 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -183,47 +237,63 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="13">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="14">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
     <cellStyle name="hdr_title" xfId="1" hidden="0"/>
     <cellStyle name="hdr_sub" xfId="2" hidden="0"/>
     <cellStyle name="section" xfId="3" hidden="0"/>
     <cellStyle name="label" xfId="4" hidden="0"/>
     <cellStyle name="value" xfId="5" hidden="0"/>
-    <cellStyle name="kpi_label" xfId="6" hidden="0"/>
-    <cellStyle name="kpi_val" xfId="7" hidden="0"/>
-    <cellStyle name="btn" xfId="8" hidden="0"/>
-    <cellStyle name="th" xfId="9" hidden="0"/>
+    <cellStyle name="input" xfId="6" hidden="0"/>
+    <cellStyle name="kpi_label" xfId="7" hidden="0"/>
+    <cellStyle name="kpi_val" xfId="8" hidden="0"/>
+    <cellStyle name="btn" xfId="9" hidden="0"/>
+    <cellStyle name="th" xfId="10" hidden="0"/>
+    <cellStyle name="th_left" xfId="11" hidden="0"/>
+    <cellStyle name="pick_id" xfId="12" hidden="0"/>
+    <cellStyle name="pick_show" xfId="13" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -324,7 +394,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!S4</f>
+              <f>'Dashboard'!S30</f>
             </strRef>
           </tx>
           <spPr>
@@ -345,12 +415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$S$5:$S$34</f>
+              <f>'Dashboard'!$S$31:$S$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -360,7 +430,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!T4</f>
+              <f>'Dashboard'!T30</f>
             </strRef>
           </tx>
           <spPr>
@@ -381,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$T$5:$T$34</f>
+              <f>'Dashboard'!$T$31:$T$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -396,7 +466,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!U4</f>
+              <f>'Dashboard'!U30</f>
             </strRef>
           </tx>
           <spPr>
@@ -417,12 +487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$U$5:$U$34</f>
+              <f>'Dashboard'!$U$31:$U$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -432,7 +502,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!V4</f>
+              <f>'Dashboard'!V30</f>
             </strRef>
           </tx>
           <spPr>
@@ -453,12 +523,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$V$5:$V$34</f>
+              <f>'Dashboard'!$V$31:$V$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -525,7 +595,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!S4</f>
+              <f>'Dashboard'!S30</f>
             </strRef>
           </tx>
           <spPr>
@@ -546,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$S$5:$S$34</f>
+              <f>'Dashboard'!$S$31:$S$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -561,7 +631,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!T4</f>
+              <f>'Dashboard'!T30</f>
             </strRef>
           </tx>
           <spPr>
@@ -582,12 +652,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$T$5:$T$34</f>
+              <f>'Dashboard'!$T$31:$T$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -597,7 +667,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!U4</f>
+              <f>'Dashboard'!U30</f>
             </strRef>
           </tx>
           <spPr>
@@ -618,12 +688,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$U$5:$U$34</f>
+              <f>'Dashboard'!$U$31:$U$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -633,7 +703,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!V4</f>
+              <f>'Dashboard'!V30</f>
             </strRef>
           </tx>
           <spPr>
@@ -654,12 +724,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$V$5:$V$34</f>
+              <f>'Dashboard'!$V$31:$V$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -726,7 +796,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!S4</f>
+              <f>'Dashboard'!S30</f>
             </strRef>
           </tx>
           <spPr>
@@ -747,12 +817,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$S$5:$S$34</f>
+              <f>'Dashboard'!$S$31:$S$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -762,7 +832,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!T4</f>
+              <f>'Dashboard'!T30</f>
             </strRef>
           </tx>
           <spPr>
@@ -783,12 +853,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$T$5:$T$34</f>
+              <f>'Dashboard'!$T$31:$T$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -798,7 +868,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!U4</f>
+              <f>'Dashboard'!U30</f>
             </strRef>
           </tx>
           <spPr>
@@ -819,12 +889,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$U$5:$U$34</f>
+              <f>'Dashboard'!$U$31:$U$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -834,7 +904,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!V4</f>
+              <f>'Dashboard'!V30</f>
             </strRef>
           </tx>
           <spPr>
@@ -855,12 +925,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$R$5:$R$34</f>
+              <f>'Dashboard'!$R$31:$R$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$V$5:$V$34</f>
+              <f>'Dashboard'!$V$31:$V$60</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -906,10 +976,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2880000"/>
+    <ext cx="5040000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -928,10 +998,10 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2880000"/>
+    <ext cx="5040000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -950,10 +1020,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2880000"/>
+    <ext cx="10080000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1292,17 +1362,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:V48"/>
+  <dimension ref="B1:AH63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -1324,12 +1394,25 @@
     <col hidden="1" width="12" customWidth="1" min="27" max="27"/>
     <col hidden="1" width="12" customWidth="1" min="28" max="28"/>
     <col hidden="1" width="12" customWidth="1" min="29" max="29"/>
-    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
-    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
-    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="12" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="12" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="12" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="12" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
-    <row r="1" ht="8" customHeight="1"/>
+    <row r="1" ht="8" customHeight="1">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Line-A</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1340,698 +1423,970 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Batch-upload CSV → filter by tag &amp; date → compare side-by-side → export report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>M01</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>M02</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>M03</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>M04</t>
+          <t>Batch-upload CSV → filter by tag &amp; date → pick machines → compare side-by-side → export report.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  FILTERS</t>
         </is>
       </c>
-      <c r="R5" s="5" t="n">
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="S5" t="n">
-        <v>53.3537992658534</v>
-      </c>
-      <c r="T5" t="n">
-        <v>55.03796564212851</v>
-      </c>
-      <c r="U5" t="n">
-        <v>57.14730967915853</v>
-      </c>
-      <c r="V5" t="n">
-        <v>62.82743051367142</v>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1">
-      <c r="R6" s="5" t="n">
-        <v>46024</v>
-      </c>
-      <c r="S6" t="n">
-        <v>51.97158987306648</v>
-      </c>
-      <c r="T6" t="n">
-        <v>56.11874561685113</v>
-      </c>
-      <c r="U6" t="n">
-        <v>60.25639929338514</v>
-      </c>
-      <c r="V6" t="n">
-        <v>63.60559634629396</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>46023</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Tag Group</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Line-A</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>▸  IMPORT CSV</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>▸  GENERATE REPORT</t>
         </is>
       </c>
-      <c r="R7" s="5" t="n">
-        <v>46025</v>
-      </c>
-      <c r="S7" t="n">
-        <v>55.77072753249099</v>
-      </c>
-      <c r="T7" t="n">
-        <v>56.32781996809334</v>
-      </c>
-      <c r="U7" t="n">
-        <v>58.16666397135825</v>
-      </c>
-      <c r="V7" t="n">
-        <v>63.20903898377193</v>
-      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="5" t="n">
         <v>46052</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Metric Focus</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Metric 1</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>▸  REFRESH DASHBOARD</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>▸  CLEAR DATA</t>
         </is>
       </c>
-      <c r="R8" s="5" t="n">
-        <v>46026</v>
-      </c>
-      <c r="S8" t="n">
-        <v>56.68803768863608</v>
-      </c>
-      <c r="T8" t="n">
-        <v>57.02729114951445</v>
-      </c>
-      <c r="U8" t="n">
-        <v>61.11559259879971</v>
-      </c>
-      <c r="V8" t="n">
-        <v>65.36982684164443</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="R9" s="5" t="n">
-        <v>46027</v>
-      </c>
-      <c r="S9" t="n">
-        <v>55.79163910355592</v>
-      </c>
-      <c r="T9" t="n">
-        <v>59.62636745331859</v>
-      </c>
-      <c r="U9" t="n">
-        <v>63.95263354331465</v>
-      </c>
-      <c r="V9" t="n">
-        <v>65.01516796574808</v>
-      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  KEY  METRICS  (filtered)</t>
         </is>
       </c>
-      <c r="R10" s="5" t="n">
-        <v>46028</v>
-      </c>
-      <c r="S10" t="n">
-        <v>57.4476261685295</v>
-      </c>
-      <c r="T10" t="n">
-        <v>58.36194280653123</v>
-      </c>
-      <c r="U10" t="n">
-        <v>62.57543080279694</v>
-      </c>
-      <c r="V10" t="n">
-        <v>65.3400682554832</v>
-      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  MACHINES</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DATA POINTS</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  AVG METRIC 1</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  AVG METRIC 2</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  AVG METRIC 3</t>
         </is>
       </c>
-      <c r="R11" s="5" t="n">
-        <v>46029</v>
-      </c>
-      <c r="S11" t="n">
-        <v>56.0590725363114</v>
-      </c>
-      <c r="T11" t="n">
-        <v>60.14038292063503</v>
-      </c>
-      <c r="U11" t="n">
-        <v>65.5845879647251</v>
-      </c>
-      <c r="V11" t="n">
-        <v>67.47467098778664</v>
-      </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="B12" s="10">
+      <c r="B12" s="8">
         <f>SUMPRODUCT((Config!D5:D20=G7)*(Config!H5:H20="Yes"))</f>
         <v/>
       </c>
-      <c r="E12" s="11">
-        <f>SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1))</f>
+      <c r="E12" s="9">
+        <f>SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1))</f>
         <v/>
       </c>
-      <c r="H12" s="12">
-        <f>IFERROR(SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1)*Data!E5:E10000)/MAX(1,SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1))),0)</f>
+      <c r="H12" s="10">
+        <f>IFERROR(SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1)*Data!E5:E20000)/MAX(1,SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1))),0)</f>
         <v/>
       </c>
-      <c r="K12" s="12">
-        <f>IFERROR(SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1)*Data!F5:F10000)/MAX(1,SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1))),0)</f>
+      <c r="K12" s="10">
+        <f>IFERROR(SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1)*Data!F5:F20000)/MAX(1,SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1))),0)</f>
         <v/>
       </c>
-      <c r="N12" s="12">
-        <f>IFERROR(SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1)*Data!G5:G10000)/MAX(1,SUMPRODUCT((Data!C5:C10000=G7)*(Data!D5:D10000&gt;=C7)*(Data!D5:D10000&lt;=C8+1))),0)</f>
+      <c r="N12" s="10">
+        <f>IFERROR(SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1)*Data!G5:G20000)/MAX(1,SUMPRODUCT((Data!C5:C20000=G7)*(Data!D5:D20000&gt;=C7)*(Data!D5:D20000&lt;=C8+1))),0)</f>
         <v/>
       </c>
-      <c r="R12" s="5" t="n">
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADD  NEW  MACHINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Machine ID</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Machine Name</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Metric 1 Name</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Metric 2 Name</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>Metric 3 Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr"/>
+      <c r="H16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="L16" s="12" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>▸  ADD MACHINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MACHINES  TO  COMPARE   (tick / untick, then REFRESH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Machine ID</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Machine Name</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Machine ID</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Machine Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Machine 01</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tip: change the Tag Group above</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Machine 02</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  then click REFRESH DASHBOARD to</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Machine 03</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  re-populate this machine list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Machine 04</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Untick any machine you want</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to exclude from the charts,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  then click REFRESH again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SIDE-BY-SIDE  COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="R30" s="13" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="S30" s="13" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="T30" s="13" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="U30" s="13" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="R31" s="16" t="n">
+        <v>46023</v>
+      </c>
+      <c r="S31" t="n">
+        <v>53.41839799793713</v>
+      </c>
+      <c r="T31" t="n">
+        <v>53.36701063695016</v>
+      </c>
+      <c r="U31" t="n">
+        <v>57.60101019510487</v>
+      </c>
+      <c r="V31" t="n">
+        <v>59.20532520495888</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="R32" s="16" t="n">
+        <v>46024</v>
+      </c>
+      <c r="S32" t="n">
+        <v>51.17332826506343</v>
+      </c>
+      <c r="T32" t="n">
+        <v>55.04916202433444</v>
+      </c>
+      <c r="U32" t="n">
+        <v>60.82745572734721</v>
+      </c>
+      <c r="V32" t="n">
+        <v>61.7775070559839</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="R33" s="16" t="n">
+        <v>46025</v>
+      </c>
+      <c r="S33" t="n">
+        <v>53.52028984722152</v>
+      </c>
+      <c r="T33" t="n">
+        <v>58.89180935545418</v>
+      </c>
+      <c r="U33" t="n">
+        <v>59.86315485764997</v>
+      </c>
+      <c r="V33" t="n">
+        <v>64.60233632666362</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="R34" s="16" t="n">
+        <v>46026</v>
+      </c>
+      <c r="S34" t="n">
+        <v>53.06416435285946</v>
+      </c>
+      <c r="T34" t="n">
+        <v>58.25470392482553</v>
+      </c>
+      <c r="U34" t="n">
+        <v>60.34923157643306</v>
+      </c>
+      <c r="V34" t="n">
+        <v>63.41290948272466</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="16" t="n">
+        <v>46027</v>
+      </c>
+      <c r="S35" t="n">
+        <v>56.51201085434686</v>
+      </c>
+      <c r="T35" t="n">
+        <v>60.61761323223188</v>
+      </c>
+      <c r="U35" t="n">
+        <v>60.31384449651578</v>
+      </c>
+      <c r="V35" t="n">
+        <v>65.48078782945359</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="16" t="n">
+        <v>46028</v>
+      </c>
+      <c r="S36" t="n">
+        <v>57.65119311310331</v>
+      </c>
+      <c r="T36" t="n">
+        <v>59.68007200997789</v>
+      </c>
+      <c r="U36" t="n">
+        <v>63.56721642443717</v>
+      </c>
+      <c r="V36" t="n">
+        <v>66.24757132201577</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="16" t="n">
+        <v>46029</v>
+      </c>
+      <c r="S37" t="n">
+        <v>58.73220393121895</v>
+      </c>
+      <c r="T37" t="n">
+        <v>60.80340188807277</v>
+      </c>
+      <c r="U37" t="n">
+        <v>65.59981980180167</v>
+      </c>
+      <c r="V37" t="n">
+        <v>68.60159144384043</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="16" t="n">
         <v>46030</v>
       </c>
-      <c r="S12" t="n">
-        <v>52.8112962540438</v>
-      </c>
-      <c r="T12" t="n">
-        <v>53.1105778407417</v>
-      </c>
-      <c r="U12" t="n">
-        <v>58.8997947951492</v>
-      </c>
-      <c r="V12" t="n">
-        <v>60.46381230086912</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="R13" s="5" t="n">
+      <c r="S38" t="n">
+        <v>52.59459993768545</v>
+      </c>
+      <c r="T38" t="n">
+        <v>55.663404011457</v>
+      </c>
+      <c r="U38" t="n">
+        <v>59.76043968780395</v>
+      </c>
+      <c r="V38" t="n">
+        <v>62.0723119319434</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="R39" s="16" t="n">
         <v>46031</v>
       </c>
-      <c r="S13" t="n">
-        <v>54.65025811403299</v>
-      </c>
-      <c r="T13" t="n">
-        <v>54.37608975449693</v>
-      </c>
-      <c r="U13" t="n">
-        <v>59.15376944945271</v>
-      </c>
-      <c r="V13" t="n">
-        <v>61.25724058098996</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SIDE-BY-SIDE  COMPARISON  (machines in selected tag group)</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="n">
+      <c r="S39" t="n">
+        <v>53.1660078209622</v>
+      </c>
+      <c r="T39" t="n">
+        <v>54.96678330757157</v>
+      </c>
+      <c r="U39" t="n">
+        <v>60.96102974982463</v>
+      </c>
+      <c r="V39" t="n">
+        <v>60.92911468473857</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="R40" s="16" t="n">
         <v>46032</v>
       </c>
-      <c r="S14" t="n">
-        <v>55.46681483039202</v>
-      </c>
-      <c r="T14" t="n">
-        <v>56.85909155885657</v>
-      </c>
-      <c r="U14" t="n">
-        <v>61.61575599409983</v>
-      </c>
-      <c r="V14" t="n">
-        <v>61.56960933232412</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="R15" s="5" t="n">
+      <c r="S40" t="n">
+        <v>53.50358888263532</v>
+      </c>
+      <c r="T40" t="n">
+        <v>55.96819511869126</v>
+      </c>
+      <c r="U40" t="n">
+        <v>61.82861267266875</v>
+      </c>
+      <c r="V40" t="n">
+        <v>64.27808653602978</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="16" t="n">
         <v>46033</v>
       </c>
-      <c r="S15" t="n">
-        <v>53.1796927755956</v>
-      </c>
-      <c r="T15" t="n">
-        <v>56.10822877364349</v>
-      </c>
-      <c r="U15" t="n">
-        <v>61.6159459828496</v>
-      </c>
-      <c r="V15" t="n">
-        <v>65.5373090898067</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="R16" s="5" t="n">
+      <c r="S41" t="n">
+        <v>53.19482569981147</v>
+      </c>
+      <c r="T41" t="n">
+        <v>58.84210469463325</v>
+      </c>
+      <c r="U41" t="n">
+        <v>62.83979927963554</v>
+      </c>
+      <c r="V41" t="n">
+        <v>63.6055991568516</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="R42" s="16" t="n">
         <v>46034</v>
       </c>
-      <c r="S16" t="n">
-        <v>57.24070652087485</v>
-      </c>
-      <c r="T16" t="n">
-        <v>59.78482214065732</v>
-      </c>
-      <c r="U16" t="n">
-        <v>61.07689768406334</v>
-      </c>
-      <c r="V16" t="n">
-        <v>65.77784455042207</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="R17" s="5" t="n">
+      <c r="S42" t="n">
+        <v>56.46898953994776</v>
+      </c>
+      <c r="T42" t="n">
+        <v>58.25608329068525</v>
+      </c>
+      <c r="U42" t="n">
+        <v>63.14208438400058</v>
+      </c>
+      <c r="V42" t="n">
+        <v>64.22672205128964</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="R43" s="16" t="n">
         <v>46035</v>
       </c>
-      <c r="S17" t="n">
-        <v>58.1531338206723</v>
-      </c>
-      <c r="T17" t="n">
-        <v>58.32508349453095</v>
-      </c>
-      <c r="U17" t="n">
-        <v>63.73004794329044</v>
-      </c>
-      <c r="V17" t="n">
-        <v>66.96181875578719</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="R18" s="5" t="n">
+      <c r="S43" t="n">
+        <v>56.15237018426664</v>
+      </c>
+      <c r="T43" t="n">
+        <v>59.21151624488067</v>
+      </c>
+      <c r="U43" t="n">
+        <v>62.91498162414297</v>
+      </c>
+      <c r="V43" t="n">
+        <v>67.42147444007557</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="R44" s="16" t="n">
         <v>46036</v>
       </c>
-      <c r="S18" t="n">
-        <v>58.75474898783334</v>
-      </c>
-      <c r="T18" t="n">
-        <v>60.47697249548839</v>
-      </c>
-      <c r="U18" t="n">
-        <v>62.60501307756311</v>
-      </c>
-      <c r="V18" t="n">
-        <v>65.04885886489365</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="R19" s="5" t="n">
+      <c r="S44" t="n">
+        <v>56.25167590093223</v>
+      </c>
+      <c r="T44" t="n">
+        <v>61.67957799295456</v>
+      </c>
+      <c r="U44" t="n">
+        <v>62.59145523385376</v>
+      </c>
+      <c r="V44" t="n">
+        <v>67.01246147065864</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="R45" s="16" t="n">
         <v>46037</v>
       </c>
-      <c r="S19" t="n">
-        <v>50.37317614220692</v>
-      </c>
-      <c r="T19" t="n">
-        <v>54.45287341358022</v>
-      </c>
-      <c r="U19" t="n">
-        <v>57.62701171073876</v>
-      </c>
-      <c r="V19" t="n">
-        <v>60.69945306695413</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="R20" s="5" t="n">
+      <c r="S45" t="n">
+        <v>50.34524914419579</v>
+      </c>
+      <c r="T45" t="n">
+        <v>54.078522001474</v>
+      </c>
+      <c r="U45" t="n">
+        <v>56.20992083213869</v>
+      </c>
+      <c r="V45" t="n">
+        <v>61.6100347318047</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="R46" s="16" t="n">
         <v>46038</v>
       </c>
-      <c r="S20" t="n">
-        <v>54.7234671946952</v>
-      </c>
-      <c r="T20" t="n">
-        <v>54.36623868634802</v>
-      </c>
-      <c r="U20" t="n">
-        <v>59.08637135524592</v>
-      </c>
-      <c r="V20" t="n">
-        <v>60.85191976818354</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="R21" s="5" t="n">
+      <c r="S46" t="n">
+        <v>54.99686342569928</v>
+      </c>
+      <c r="T46" t="n">
+        <v>54.60884334989882</v>
+      </c>
+      <c r="U46" t="n">
+        <v>60.34486989697078</v>
+      </c>
+      <c r="V46" t="n">
+        <v>62.14014692047522</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="R47" s="16" t="n">
         <v>46039</v>
       </c>
-      <c r="S21" t="n">
-        <v>52.08844621773734</v>
-      </c>
-      <c r="T21" t="n">
-        <v>55.86469656941571</v>
-      </c>
-      <c r="U21" t="n">
-        <v>59.71531142652159</v>
-      </c>
-      <c r="V21" t="n">
-        <v>61.59216029353308</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="R22" s="5" t="n">
+      <c r="S47" t="n">
+        <v>53.1319825544658</v>
+      </c>
+      <c r="T47" t="n">
+        <v>58.5466979661727</v>
+      </c>
+      <c r="U47" t="n">
+        <v>61.3362799631792</v>
+      </c>
+      <c r="V47" t="n">
+        <v>62.78717122617198</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="R48" s="16" t="n">
         <v>46040</v>
       </c>
-      <c r="S22" t="n">
-        <v>53.55861684048185</v>
-      </c>
-      <c r="T22" t="n">
-        <v>58.18863291303998</v>
-      </c>
-      <c r="U22" t="n">
-        <v>62.44409788214364</v>
-      </c>
-      <c r="V22" t="n">
-        <v>63.75230913337247</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="R23" s="5" t="n">
+      <c r="S48" t="n">
+        <v>56.1487394524057</v>
+      </c>
+      <c r="T48" t="n">
+        <v>56.25040653907688</v>
+      </c>
+      <c r="U48" t="n">
+        <v>62.12723296855119</v>
+      </c>
+      <c r="V48" t="n">
+        <v>64.57939627140716</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="R49" s="16" t="n">
         <v>46041</v>
       </c>
-      <c r="S23" t="n">
-        <v>54.27020568217394</v>
-      </c>
-      <c r="T23" t="n">
-        <v>58.24503811846154</v>
-      </c>
-      <c r="U23" t="n">
-        <v>62.95582915807537</v>
-      </c>
-      <c r="V23" t="n">
-        <v>65.26025104303197</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="R24" s="5" t="n">
+      <c r="S49" t="n">
+        <v>56.64394502797337</v>
+      </c>
+      <c r="T49" t="n">
+        <v>57.6481374930007</v>
+      </c>
+      <c r="U49" t="n">
+        <v>62.65350546619855</v>
+      </c>
+      <c r="V49" t="n">
+        <v>63.44738202404343</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="R50" s="16" t="n">
         <v>46042</v>
       </c>
-      <c r="S24" t="n">
-        <v>55.25968799420683</v>
-      </c>
-      <c r="T24" t="n">
-        <v>59.21709831322771</v>
-      </c>
-      <c r="U24" t="n">
-        <v>61.49944880034496</v>
-      </c>
-      <c r="V24" t="n">
-        <v>67.50458703845477</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="R25" s="5" t="n">
+      <c r="S50" t="n">
+        <v>56.90399019072311</v>
+      </c>
+      <c r="T50" t="n">
+        <v>58.17150035764118</v>
+      </c>
+      <c r="U50" t="n">
+        <v>63.44311199172137</v>
+      </c>
+      <c r="V50" t="n">
+        <v>64.31285102969299</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="R51" s="16" t="n">
         <v>46043</v>
       </c>
-      <c r="S25" t="n">
-        <v>58.85305385753422</v>
-      </c>
-      <c r="T25" t="n">
-        <v>61.85820106384815</v>
-      </c>
-      <c r="U25" t="n">
-        <v>63.14992228082219</v>
-      </c>
-      <c r="V25" t="n">
-        <v>68.23969391901205</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="R26" s="5" t="n">
+      <c r="S51" t="n">
+        <v>58.1058561201589</v>
+      </c>
+      <c r="T51" t="n">
+        <v>62.37379501964885</v>
+      </c>
+      <c r="U51" t="n">
+        <v>62.95735068383451</v>
+      </c>
+      <c r="V51" t="n">
+        <v>68.8803420659447</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="R52" s="16" t="n">
         <v>46044</v>
       </c>
-      <c r="S26" t="n">
-        <v>50.75411048569148</v>
-      </c>
-      <c r="T26" t="n">
-        <v>56.46697894097834</v>
-      </c>
-      <c r="U26" t="n">
-        <v>57.55140168657899</v>
-      </c>
-      <c r="V26" t="n">
-        <v>59.31669430259318</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="R27" s="5" t="n">
+      <c r="S52" t="n">
+        <v>50.9780643155559</v>
+      </c>
+      <c r="T52" t="n">
+        <v>55.34242530714955</v>
+      </c>
+      <c r="U52" t="n">
+        <v>56.10406862103346</v>
+      </c>
+      <c r="V52" t="n">
+        <v>62.2556895735304</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="R53" s="16" t="n">
         <v>46045</v>
       </c>
-      <c r="S27" t="n">
-        <v>51.41899236003228</v>
-      </c>
-      <c r="T27" t="n">
-        <v>55.79318904535472</v>
-      </c>
-      <c r="U27" t="n">
-        <v>57.67047707390236</v>
-      </c>
-      <c r="V27" t="n">
-        <v>61.23267266077816</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="R28" s="5" t="n">
+      <c r="S53" t="n">
+        <v>53.5537992501031</v>
+      </c>
+      <c r="T53" t="n">
+        <v>55.94861147925529</v>
+      </c>
+      <c r="U53" t="n">
+        <v>60.83617043709796</v>
+      </c>
+      <c r="V53" t="n">
+        <v>63.3397928476164</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="R54" s="16" t="n">
         <v>46046</v>
       </c>
-      <c r="S28" t="n">
-        <v>52.70616448677988</v>
-      </c>
-      <c r="T28" t="n">
-        <v>55.71254832491203</v>
-      </c>
-      <c r="U28" t="n">
-        <v>61.61006213682977</v>
-      </c>
-      <c r="V28" t="n">
-        <v>61.2374273365617</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="R29" s="5" t="n">
+      <c r="S54" t="n">
+        <v>55.18418595476253</v>
+      </c>
+      <c r="T54" t="n">
+        <v>55.21862700877913</v>
+      </c>
+      <c r="U54" t="n">
+        <v>61.71543648041506</v>
+      </c>
+      <c r="V54" t="n">
+        <v>61.95654867820362</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="R55" s="16" t="n">
         <v>46047</v>
       </c>
-      <c r="S29" t="n">
-        <v>54.53022675271487</v>
-      </c>
-      <c r="T29" t="n">
-        <v>57.86548361409523</v>
-      </c>
-      <c r="U29" t="n">
-        <v>60.65040949888132</v>
-      </c>
-      <c r="V29" t="n">
-        <v>62.44747826348782</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="R30" s="5" t="n">
+      <c r="S55" t="n">
+        <v>53.21492137139455</v>
+      </c>
+      <c r="T55" t="n">
+        <v>57.84103942146656</v>
+      </c>
+      <c r="U55" t="n">
+        <v>62.02550060619232</v>
+      </c>
+      <c r="V55" t="n">
+        <v>62.24823983372207</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="R56" s="16" t="n">
         <v>46048</v>
       </c>
-      <c r="S30" t="n">
-        <v>54.09945720557825</v>
-      </c>
-      <c r="T30" t="n">
-        <v>57.5256830691497</v>
-      </c>
-      <c r="U30" t="n">
-        <v>61.25213194178117</v>
-      </c>
-      <c r="V30" t="n">
-        <v>66.42637163813514</v>
-      </c>
-    </row>
-    <row r="31" ht="8" customHeight="1">
-      <c r="R31" s="5" t="n">
+      <c r="S56" t="n">
+        <v>57.11870383102601</v>
+      </c>
+      <c r="T56" t="n">
+        <v>60.69814556879862</v>
+      </c>
+      <c r="U56" t="n">
+        <v>61.8930784494557</v>
+      </c>
+      <c r="V56" t="n">
+        <v>64.31888090927076</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="R57" s="16" t="n">
         <v>46049</v>
       </c>
-      <c r="S31" t="n">
-        <v>57.95613358379495</v>
-      </c>
-      <c r="T31" t="n">
-        <v>60.69818961291168</v>
-      </c>
-      <c r="U31" t="n">
-        <v>62.7629908673112</v>
-      </c>
-      <c r="V31" t="n">
-        <v>67.86677725547609</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="R32" s="5" t="n">
+      <c r="S57" t="n">
+        <v>58.09653959703112</v>
+      </c>
+      <c r="T57" t="n">
+        <v>58.78031772817177</v>
+      </c>
+      <c r="U57" t="n">
+        <v>63.74867739144806</v>
+      </c>
+      <c r="V57" t="n">
+        <v>66.02262944967426</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="R58" s="16" t="n">
         <v>46050</v>
       </c>
-      <c r="S32" t="n">
-        <v>58.02058439321043</v>
-      </c>
-      <c r="T32" t="n">
-        <v>62.22048193064895</v>
-      </c>
-      <c r="U32" t="n">
-        <v>62.54562861266718</v>
-      </c>
-      <c r="V32" t="n">
-        <v>66.44187278389553</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="R33" s="5" t="n">
+      <c r="S58" t="n">
+        <v>57.33370220340375</v>
+      </c>
+      <c r="T58" t="n">
+        <v>60.22417486235164</v>
+      </c>
+      <c r="U58" t="n">
+        <v>64.13849577985324</v>
+      </c>
+      <c r="V58" t="n">
+        <v>66.28172135930463</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="R59" s="16" t="n">
         <v>46051</v>
       </c>
-      <c r="S33" t="n">
-        <v>51.79352497701284</v>
-      </c>
-      <c r="T33" t="n">
-        <v>55.8170997149391</v>
-      </c>
-      <c r="U33" t="n">
-        <v>56.77948267390975</v>
-      </c>
-      <c r="V33" t="n">
-        <v>61.46753817058597</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="R34" s="5" t="n">
+      <c r="S59" t="n">
+        <v>50.14314032645305</v>
+      </c>
+      <c r="T59" t="n">
+        <v>55.89395255231344</v>
+      </c>
+      <c r="U59" t="n">
+        <v>59.64367702912718</v>
+      </c>
+      <c r="V59" t="n">
+        <v>61.61075390596538</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="R60" s="16" t="n">
         <v>46052</v>
       </c>
-      <c r="S34" t="n">
-        <v>54.84910795678509</v>
-      </c>
-      <c r="T34" t="n">
-        <v>56.91870164639594</v>
-      </c>
-      <c r="U34" t="n">
-        <v>60.5267162935172</v>
-      </c>
-      <c r="V34" t="n">
-        <v>63.60850732453755</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TIP: change filters, then press REFRESH. Ctrl+Shift+I = Import, Ctrl+Shift+R = Refresh, Ctrl+Shift+G = Generate Report.</t>
+      <c r="S60" t="n">
+        <v>53.82449709190025</v>
+      </c>
+      <c r="T60" t="n">
+        <v>55.83656246868125</v>
+      </c>
+      <c r="U60" t="n">
+        <v>58.51955209209009</v>
+      </c>
+      <c r="V60" t="n">
+        <v>61.35664486587278</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TIP: Ctrl+Shift+I = Import   |   Ctrl+Shift+R = Refresh   |   Ctrl+Shift+G = Generate Report</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="45">
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B48:P48"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L16:M16"/>
     <mergeCell ref="B14:P14"/>
+    <mergeCell ref="J21:P21"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="H11:J11"/>
+    <mergeCell ref="B18:P18"/>
     <mergeCell ref="J7:L7"/>
+    <mergeCell ref="B29:P29"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="B10:P10"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
     <mergeCell ref="H12:J12"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
     <mergeCell ref="B5:P5"/>
+    <mergeCell ref="B63:P63"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="E12:G12"/>
+    <mergeCell ref="J24:P24"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="N11:P11"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="B3:P3"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J20:P20"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="K11:M11"/>
+    <mergeCell ref="J25:P25"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="G7:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=Config!$D$5:$D$20</formula1>
     </dataValidation>
     <dataValidation sqref="G8:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Metric 1,Metric 2,Metric 3,All"</formula1>
+      <formula1>"Metric 1,Metric 2,Metric 3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20 B21 B22 B23 B24 B25 B26 B27 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2074,629 +2429,629 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Machine ID</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Machine Name</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Metric 1 Name</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Metric 2 Name</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Metric 3 Name</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Machine 01</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Line-A</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Temperature (°C)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Vibration (mm/s)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Output (units/h)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Machine 02</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Line-A</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Temperature (°C)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Vibration (mm/s)</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Output (units/h)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Machine 03</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Line-A</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Temperature (°C)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Vibration (mm/s)</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Output (units/h)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Machine 04</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Line-A</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Temperature (°C)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Vibration (mm/s)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Output (units/h)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Machine 05</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Line-B</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Pressure (bar)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Flow (L/min)</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>M06</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Machine 06</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Line-B</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Pressure (bar)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Flow (L/min)</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>M07</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Machine 07</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Line-B</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Pressure (bar)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Flow (L/min)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>M08</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Machine 08</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Line-B</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Pressure (bar)</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Flow (L/min)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>M09</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Machine 09</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Line-C</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Torque (Nm)</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Current (A)</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Voltage (V)</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Machine 10</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Line-C</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Torque (Nm)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Current (A)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Voltage (V)</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Machine 11</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Line-C</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Torque (Nm)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Current (A)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Voltage (V)</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Machine 12</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Line-C</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Torque (Nm)</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Current (A)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Voltage (V)</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Machine 13</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Line-D</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Speed (m/s)</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Load (%)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Cycles/hr</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Machine 14</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Line-D</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Speed (m/s)</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Load (%)</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Cycles/hr</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>M15</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Machine 15</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Line-D</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Speed (m/s)</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Load (%)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Cycles/hr</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Machine 16</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Line-D</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Speed (m/s)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Load (%)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Cycles/hr</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2753,32 +3108,32 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Machine ID</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Metric 1</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Metric 2</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Metric 3</t>
         </is>
@@ -2795,7 +3150,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E5" t="n">
@@ -2819,7 +3174,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E6" t="n">
@@ -2843,7 +3198,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E7" t="n">
@@ -2867,7 +3222,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E8" t="n">
@@ -2891,7 +3246,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E9" t="n">
@@ -2915,7 +3270,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E10" t="n">
@@ -2939,7 +3294,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E11" t="n">
@@ -2963,7 +3318,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E12" t="n">
@@ -2987,7 +3342,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E13" t="n">
@@ -3011,7 +3366,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E14" t="n">
@@ -3035,7 +3390,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E15" t="n">
@@ -3059,7 +3414,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E16" t="n">
@@ -3083,7 +3438,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E17" t="n">
@@ -3107,7 +3462,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E18" t="n">
@@ -3131,7 +3486,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E19" t="n">
@@ -3155,7 +3510,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="17" t="n">
         <v>46023.33333333334</v>
       </c>
       <c r="E20" t="n">
@@ -3179,7 +3534,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E21" t="n">
@@ -3203,7 +3558,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E22" t="n">
@@ -3227,7 +3582,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E23" t="n">
@@ -3251,7 +3606,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E24" t="n">
@@ -3275,7 +3630,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E25" t="n">
@@ -3299,7 +3654,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E26" t="n">
@@ -3323,7 +3678,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E27" t="n">
@@ -3347,7 +3702,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E28" t="n">
@@ -3371,7 +3726,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E29" t="n">
@@ -3395,7 +3750,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E30" t="n">
@@ -3419,7 +3774,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E31" t="n">
@@ -3443,7 +3798,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E32" t="n">
@@ -3467,7 +3822,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E33" t="n">
@@ -3491,7 +3846,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E34" t="n">
@@ -3515,7 +3870,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E35" t="n">
@@ -3539,7 +3894,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="17" t="n">
         <v>46024.33333333334</v>
       </c>
       <c r="E36" t="n">
@@ -3563,7 +3918,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E37" t="n">
@@ -3587,7 +3942,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E38" t="n">
@@ -3611,7 +3966,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E39" t="n">
@@ -3635,7 +3990,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E40" t="n">
@@ -3659,7 +4014,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E41" t="n">
@@ -3683,7 +4038,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E42" t="n">
@@ -3707,7 +4062,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E43" t="n">
@@ -3731,7 +4086,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E44" t="n">
@@ -3755,7 +4110,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E45" t="n">
@@ -3779,7 +4134,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E46" t="n">
@@ -3803,7 +4158,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E47" t="n">
@@ -3827,7 +4182,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E48" t="n">
@@ -3851,7 +4206,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E49" t="n">
@@ -3875,7 +4230,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E50" t="n">
@@ -3899,7 +4254,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E51" t="n">
@@ -3923,7 +4278,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="17" t="n">
         <v>46025.33333333334</v>
       </c>
       <c r="E52" t="n">
@@ -3947,7 +4302,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E53" t="n">
@@ -3971,7 +4326,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E54" t="n">
@@ -3995,7 +4350,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E55" t="n">
@@ -4019,7 +4374,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E56" t="n">
@@ -4043,7 +4398,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E57" t="n">
@@ -4067,7 +4422,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E58" t="n">
@@ -4091,7 +4446,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E59" t="n">
@@ -4115,7 +4470,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E60" t="n">
@@ -4139,7 +4494,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E61" t="n">
@@ -4163,7 +4518,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E62" t="n">
@@ -4187,7 +4542,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E63" t="n">
@@ -4211,7 +4566,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E64" t="n">
@@ -4235,7 +4590,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E65" t="n">
@@ -4259,7 +4614,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E66" t="n">
@@ -4283,7 +4638,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E67" t="n">
@@ -4307,7 +4662,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="17" t="n">
         <v>46026.33333333334</v>
       </c>
       <c r="E68" t="n">
@@ -4331,7 +4686,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E69" t="n">
@@ -4355,7 +4710,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D70" s="13" t="n">
+      <c r="D70" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E70" t="n">
@@ -4379,7 +4734,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D71" s="13" t="n">
+      <c r="D71" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E71" t="n">
@@ -4403,7 +4758,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D72" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E72" t="n">
@@ -4427,7 +4782,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E73" t="n">
@@ -4451,7 +4806,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D74" s="13" t="n">
+      <c r="D74" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E74" t="n">
@@ -4475,7 +4830,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D75" s="13" t="n">
+      <c r="D75" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E75" t="n">
@@ -4499,7 +4854,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D76" s="13" t="n">
+      <c r="D76" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E76" t="n">
@@ -4523,7 +4878,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D77" s="13" t="n">
+      <c r="D77" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E77" t="n">
@@ -4547,7 +4902,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D78" s="13" t="n">
+      <c r="D78" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E78" t="n">
@@ -4571,7 +4926,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D79" s="13" t="n">
+      <c r="D79" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E79" t="n">
@@ -4595,7 +4950,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D80" s="13" t="n">
+      <c r="D80" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E80" t="n">
@@ -4619,7 +4974,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D81" s="13" t="n">
+      <c r="D81" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E81" t="n">
@@ -4643,7 +4998,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D82" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E82" t="n">
@@ -4667,7 +5022,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D83" s="13" t="n">
+      <c r="D83" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E83" t="n">
@@ -4691,7 +5046,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D84" s="13" t="n">
+      <c r="D84" s="17" t="n">
         <v>46027.33333333334</v>
       </c>
       <c r="E84" t="n">
@@ -4715,7 +5070,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D85" s="13" t="n">
+      <c r="D85" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E85" t="n">
@@ -4739,7 +5094,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D86" s="13" t="n">
+      <c r="D86" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E86" t="n">
@@ -4763,7 +5118,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D87" s="13" t="n">
+      <c r="D87" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E87" t="n">
@@ -4787,7 +5142,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D88" s="13" t="n">
+      <c r="D88" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E88" t="n">
@@ -4811,7 +5166,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D89" s="13" t="n">
+      <c r="D89" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E89" t="n">
@@ -4835,7 +5190,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D90" s="13" t="n">
+      <c r="D90" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E90" t="n">
@@ -4859,7 +5214,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D91" s="13" t="n">
+      <c r="D91" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E91" t="n">
@@ -4883,7 +5238,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D92" s="13" t="n">
+      <c r="D92" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E92" t="n">
@@ -4907,7 +5262,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D93" s="13" t="n">
+      <c r="D93" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E93" t="n">
@@ -4931,7 +5286,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D94" s="13" t="n">
+      <c r="D94" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E94" t="n">
@@ -4955,7 +5310,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D95" s="13" t="n">
+      <c r="D95" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E95" t="n">
@@ -4979,7 +5334,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D96" s="13" t="n">
+      <c r="D96" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E96" t="n">
@@ -5003,7 +5358,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D97" s="13" t="n">
+      <c r="D97" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E97" t="n">
@@ -5027,7 +5382,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D98" s="13" t="n">
+      <c r="D98" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E98" t="n">
@@ -5051,7 +5406,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D99" s="13" t="n">
+      <c r="D99" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E99" t="n">
@@ -5075,7 +5430,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D100" s="13" t="n">
+      <c r="D100" s="17" t="n">
         <v>46028.33333333334</v>
       </c>
       <c r="E100" t="n">
@@ -5099,7 +5454,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D101" s="13" t="n">
+      <c r="D101" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E101" t="n">
@@ -5123,7 +5478,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D102" s="13" t="n">
+      <c r="D102" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E102" t="n">
@@ -5147,7 +5502,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D103" s="13" t="n">
+      <c r="D103" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E103" t="n">
@@ -5171,7 +5526,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D104" s="13" t="n">
+      <c r="D104" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E104" t="n">
@@ -5195,7 +5550,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D105" s="13" t="n">
+      <c r="D105" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E105" t="n">
@@ -5219,7 +5574,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D106" s="13" t="n">
+      <c r="D106" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E106" t="n">
@@ -5243,7 +5598,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D107" s="13" t="n">
+      <c r="D107" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E107" t="n">
@@ -5267,7 +5622,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D108" s="13" t="n">
+      <c r="D108" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E108" t="n">
@@ -5291,7 +5646,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D109" s="13" t="n">
+      <c r="D109" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E109" t="n">
@@ -5315,7 +5670,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D110" s="13" t="n">
+      <c r="D110" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E110" t="n">
@@ -5339,7 +5694,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D111" s="13" t="n">
+      <c r="D111" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E111" t="n">
@@ -5363,7 +5718,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D112" s="13" t="n">
+      <c r="D112" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E112" t="n">
@@ -5387,7 +5742,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D113" s="13" t="n">
+      <c r="D113" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E113" t="n">
@@ -5411,7 +5766,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D114" s="13" t="n">
+      <c r="D114" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E114" t="n">
@@ -5435,7 +5790,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D115" s="13" t="n">
+      <c r="D115" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E115" t="n">
@@ -5459,7 +5814,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D116" s="13" t="n">
+      <c r="D116" s="17" t="n">
         <v>46029.33333333334</v>
       </c>
       <c r="E116" t="n">
@@ -5483,7 +5838,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D117" s="13" t="n">
+      <c r="D117" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E117" t="n">
@@ -5507,7 +5862,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D118" s="13" t="n">
+      <c r="D118" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E118" t="n">
@@ -5531,7 +5886,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D119" s="13" t="n">
+      <c r="D119" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E119" t="n">
@@ -5555,7 +5910,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D120" s="13" t="n">
+      <c r="D120" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E120" t="n">
@@ -5579,7 +5934,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D121" s="13" t="n">
+      <c r="D121" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E121" t="n">
@@ -5603,7 +5958,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D122" s="13" t="n">
+      <c r="D122" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E122" t="n">
@@ -5627,7 +5982,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D123" s="13" t="n">
+      <c r="D123" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E123" t="n">
@@ -5651,7 +6006,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D124" s="13" t="n">
+      <c r="D124" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E124" t="n">
@@ -5675,7 +6030,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D125" s="13" t="n">
+      <c r="D125" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E125" t="n">
@@ -5699,7 +6054,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D126" s="13" t="n">
+      <c r="D126" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E126" t="n">
@@ -5723,7 +6078,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D127" s="13" t="n">
+      <c r="D127" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E127" t="n">
@@ -5747,7 +6102,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D128" s="13" t="n">
+      <c r="D128" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E128" t="n">
@@ -5771,7 +6126,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D129" s="13" t="n">
+      <c r="D129" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E129" t="n">
@@ -5795,7 +6150,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D130" s="13" t="n">
+      <c r="D130" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E130" t="n">
@@ -5819,7 +6174,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D131" s="13" t="n">
+      <c r="D131" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E131" t="n">
@@ -5843,7 +6198,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D132" s="13" t="n">
+      <c r="D132" s="17" t="n">
         <v>46030.33333333334</v>
       </c>
       <c r="E132" t="n">
@@ -5867,7 +6222,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D133" s="13" t="n">
+      <c r="D133" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E133" t="n">
@@ -5891,7 +6246,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D134" s="13" t="n">
+      <c r="D134" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E134" t="n">
@@ -5915,7 +6270,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D135" s="13" t="n">
+      <c r="D135" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E135" t="n">
@@ -5939,7 +6294,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D136" s="13" t="n">
+      <c r="D136" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E136" t="n">
@@ -5963,7 +6318,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D137" s="13" t="n">
+      <c r="D137" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E137" t="n">
@@ -5987,7 +6342,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D138" s="13" t="n">
+      <c r="D138" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E138" t="n">
@@ -6011,7 +6366,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D139" s="13" t="n">
+      <c r="D139" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E139" t="n">
@@ -6035,7 +6390,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D140" s="13" t="n">
+      <c r="D140" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E140" t="n">
@@ -6059,7 +6414,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D141" s="13" t="n">
+      <c r="D141" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E141" t="n">
@@ -6083,7 +6438,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D142" s="13" t="n">
+      <c r="D142" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E142" t="n">
@@ -6107,7 +6462,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D143" s="13" t="n">
+      <c r="D143" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E143" t="n">
@@ -6131,7 +6486,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D144" s="13" t="n">
+      <c r="D144" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E144" t="n">
@@ -6155,7 +6510,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D145" s="13" t="n">
+      <c r="D145" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E145" t="n">
@@ -6179,7 +6534,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D146" s="13" t="n">
+      <c r="D146" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E146" t="n">
@@ -6203,7 +6558,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D147" s="13" t="n">
+      <c r="D147" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E147" t="n">
@@ -6227,7 +6582,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D148" s="13" t="n">
+      <c r="D148" s="17" t="n">
         <v>46031.33333333334</v>
       </c>
       <c r="E148" t="n">
@@ -6251,7 +6606,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D149" s="13" t="n">
+      <c r="D149" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E149" t="n">
@@ -6275,7 +6630,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D150" s="13" t="n">
+      <c r="D150" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E150" t="n">
@@ -6299,7 +6654,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D151" s="13" t="n">
+      <c r="D151" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E151" t="n">
@@ -6323,7 +6678,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D152" s="13" t="n">
+      <c r="D152" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E152" t="n">
@@ -6347,7 +6702,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D153" s="13" t="n">
+      <c r="D153" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E153" t="n">
@@ -6371,7 +6726,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D154" s="13" t="n">
+      <c r="D154" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E154" t="n">
@@ -6395,7 +6750,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D155" s="13" t="n">
+      <c r="D155" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E155" t="n">
@@ -6419,7 +6774,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D156" s="13" t="n">
+      <c r="D156" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E156" t="n">
@@ -6443,7 +6798,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D157" s="13" t="n">
+      <c r="D157" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E157" t="n">
@@ -6467,7 +6822,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D158" s="13" t="n">
+      <c r="D158" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E158" t="n">
@@ -6491,7 +6846,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D159" s="13" t="n">
+      <c r="D159" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E159" t="n">
@@ -6515,7 +6870,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D160" s="13" t="n">
+      <c r="D160" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E160" t="n">
@@ -6539,7 +6894,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D161" s="13" t="n">
+      <c r="D161" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E161" t="n">
@@ -6563,7 +6918,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D162" s="13" t="n">
+      <c r="D162" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E162" t="n">
@@ -6587,7 +6942,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D163" s="13" t="n">
+      <c r="D163" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E163" t="n">
@@ -6611,7 +6966,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D164" s="13" t="n">
+      <c r="D164" s="17" t="n">
         <v>46032.33333333334</v>
       </c>
       <c r="E164" t="n">
@@ -6635,7 +6990,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D165" s="13" t="n">
+      <c r="D165" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E165" t="n">
@@ -6659,7 +7014,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D166" s="13" t="n">
+      <c r="D166" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E166" t="n">
@@ -6683,7 +7038,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D167" s="13" t="n">
+      <c r="D167" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E167" t="n">
@@ -6707,7 +7062,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D168" s="13" t="n">
+      <c r="D168" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E168" t="n">
@@ -6731,7 +7086,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D169" s="13" t="n">
+      <c r="D169" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E169" t="n">
@@ -6755,7 +7110,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D170" s="13" t="n">
+      <c r="D170" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E170" t="n">
@@ -6779,7 +7134,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D171" s="13" t="n">
+      <c r="D171" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E171" t="n">
@@ -6803,7 +7158,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D172" s="13" t="n">
+      <c r="D172" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E172" t="n">
@@ -6827,7 +7182,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D173" s="13" t="n">
+      <c r="D173" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E173" t="n">
@@ -6851,7 +7206,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D174" s="13" t="n">
+      <c r="D174" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E174" t="n">
@@ -6875,7 +7230,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D175" s="13" t="n">
+      <c r="D175" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E175" t="n">
@@ -6899,7 +7254,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D176" s="13" t="n">
+      <c r="D176" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E176" t="n">
@@ -6923,7 +7278,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D177" s="13" t="n">
+      <c r="D177" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E177" t="n">
@@ -6947,7 +7302,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D178" s="13" t="n">
+      <c r="D178" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E178" t="n">
@@ -6971,7 +7326,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D179" s="13" t="n">
+      <c r="D179" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E179" t="n">
@@ -6995,7 +7350,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D180" s="13" t="n">
+      <c r="D180" s="17" t="n">
         <v>46033.33333333334</v>
       </c>
       <c r="E180" t="n">
@@ -7019,7 +7374,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D181" s="13" t="n">
+      <c r="D181" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E181" t="n">
@@ -7043,7 +7398,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D182" s="13" t="n">
+      <c r="D182" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E182" t="n">
@@ -7067,7 +7422,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D183" s="13" t="n">
+      <c r="D183" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E183" t="n">
@@ -7091,7 +7446,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D184" s="13" t="n">
+      <c r="D184" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E184" t="n">
@@ -7115,7 +7470,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D185" s="13" t="n">
+      <c r="D185" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E185" t="n">
@@ -7139,7 +7494,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D186" s="13" t="n">
+      <c r="D186" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E186" t="n">
@@ -7163,7 +7518,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D187" s="13" t="n">
+      <c r="D187" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E187" t="n">
@@ -7187,7 +7542,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D188" s="13" t="n">
+      <c r="D188" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E188" t="n">
@@ -7211,7 +7566,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D189" s="13" t="n">
+      <c r="D189" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E189" t="n">
@@ -7235,7 +7590,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D190" s="13" t="n">
+      <c r="D190" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E190" t="n">
@@ -7259,7 +7614,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D191" s="13" t="n">
+      <c r="D191" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E191" t="n">
@@ -7283,7 +7638,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D192" s="13" t="n">
+      <c r="D192" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E192" t="n">
@@ -7307,7 +7662,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D193" s="13" t="n">
+      <c r="D193" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E193" t="n">
@@ -7331,7 +7686,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D194" s="13" t="n">
+      <c r="D194" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E194" t="n">
@@ -7355,7 +7710,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D195" s="13" t="n">
+      <c r="D195" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E195" t="n">
@@ -7379,7 +7734,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D196" s="13" t="n">
+      <c r="D196" s="17" t="n">
         <v>46034.33333333334</v>
       </c>
       <c r="E196" t="n">
@@ -7403,7 +7758,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D197" s="13" t="n">
+      <c r="D197" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E197" t="n">
@@ -7427,7 +7782,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D198" s="13" t="n">
+      <c r="D198" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E198" t="n">
@@ -7451,7 +7806,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D199" s="13" t="n">
+      <c r="D199" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E199" t="n">
@@ -7475,7 +7830,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D200" s="13" t="n">
+      <c r="D200" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E200" t="n">
@@ -7499,7 +7854,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D201" s="13" t="n">
+      <c r="D201" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E201" t="n">
@@ -7523,7 +7878,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D202" s="13" t="n">
+      <c r="D202" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E202" t="n">
@@ -7547,7 +7902,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D203" s="13" t="n">
+      <c r="D203" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E203" t="n">
@@ -7571,7 +7926,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D204" s="13" t="n">
+      <c r="D204" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E204" t="n">
@@ -7595,7 +7950,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D205" s="13" t="n">
+      <c r="D205" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E205" t="n">
@@ -7619,7 +7974,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D206" s="13" t="n">
+      <c r="D206" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E206" t="n">
@@ -7643,7 +7998,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D207" s="13" t="n">
+      <c r="D207" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E207" t="n">
@@ -7667,7 +8022,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D208" s="13" t="n">
+      <c r="D208" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E208" t="n">
@@ -7691,7 +8046,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D209" s="13" t="n">
+      <c r="D209" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E209" t="n">
@@ -7715,7 +8070,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D210" s="13" t="n">
+      <c r="D210" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E210" t="n">
@@ -7739,7 +8094,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D211" s="13" t="n">
+      <c r="D211" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E211" t="n">
@@ -7763,7 +8118,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D212" s="13" t="n">
+      <c r="D212" s="17" t="n">
         <v>46035.33333333334</v>
       </c>
       <c r="E212" t="n">
@@ -7787,7 +8142,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D213" s="13" t="n">
+      <c r="D213" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E213" t="n">
@@ -7811,7 +8166,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D214" s="13" t="n">
+      <c r="D214" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E214" t="n">
@@ -7835,7 +8190,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D215" s="13" t="n">
+      <c r="D215" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E215" t="n">
@@ -7859,7 +8214,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D216" s="13" t="n">
+      <c r="D216" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E216" t="n">
@@ -7883,7 +8238,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D217" s="13" t="n">
+      <c r="D217" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E217" t="n">
@@ -7907,7 +8262,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D218" s="13" t="n">
+      <c r="D218" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E218" t="n">
@@ -7931,7 +8286,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D219" s="13" t="n">
+      <c r="D219" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E219" t="n">
@@ -7955,7 +8310,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D220" s="13" t="n">
+      <c r="D220" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E220" t="n">
@@ -7979,7 +8334,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D221" s="13" t="n">
+      <c r="D221" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E221" t="n">
@@ -8003,7 +8358,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D222" s="13" t="n">
+      <c r="D222" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E222" t="n">
@@ -8027,7 +8382,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D223" s="13" t="n">
+      <c r="D223" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E223" t="n">
@@ -8051,7 +8406,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D224" s="13" t="n">
+      <c r="D224" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E224" t="n">
@@ -8075,7 +8430,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D225" s="13" t="n">
+      <c r="D225" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E225" t="n">
@@ -8099,7 +8454,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D226" s="13" t="n">
+      <c r="D226" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E226" t="n">
@@ -8123,7 +8478,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D227" s="13" t="n">
+      <c r="D227" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E227" t="n">
@@ -8147,7 +8502,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D228" s="13" t="n">
+      <c r="D228" s="17" t="n">
         <v>46036.33333333334</v>
       </c>
       <c r="E228" t="n">
@@ -8171,7 +8526,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D229" s="13" t="n">
+      <c r="D229" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E229" t="n">
@@ -8195,7 +8550,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D230" s="13" t="n">
+      <c r="D230" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E230" t="n">
@@ -8219,7 +8574,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D231" s="13" t="n">
+      <c r="D231" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E231" t="n">
@@ -8243,7 +8598,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D232" s="13" t="n">
+      <c r="D232" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E232" t="n">
@@ -8267,7 +8622,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D233" s="13" t="n">
+      <c r="D233" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E233" t="n">
@@ -8291,7 +8646,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D234" s="13" t="n">
+      <c r="D234" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E234" t="n">
@@ -8315,7 +8670,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D235" s="13" t="n">
+      <c r="D235" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E235" t="n">
@@ -8339,7 +8694,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D236" s="13" t="n">
+      <c r="D236" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E236" t="n">
@@ -8363,7 +8718,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D237" s="13" t="n">
+      <c r="D237" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E237" t="n">
@@ -8387,7 +8742,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D238" s="13" t="n">
+      <c r="D238" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E238" t="n">
@@ -8411,7 +8766,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D239" s="13" t="n">
+      <c r="D239" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E239" t="n">
@@ -8435,7 +8790,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D240" s="13" t="n">
+      <c r="D240" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E240" t="n">
@@ -8459,7 +8814,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D241" s="13" t="n">
+      <c r="D241" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E241" t="n">
@@ -8483,7 +8838,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D242" s="13" t="n">
+      <c r="D242" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E242" t="n">
@@ -8507,7 +8862,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D243" s="13" t="n">
+      <c r="D243" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E243" t="n">
@@ -8531,7 +8886,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D244" s="13" t="n">
+      <c r="D244" s="17" t="n">
         <v>46037.33333333334</v>
       </c>
       <c r="E244" t="n">
@@ -8555,7 +8910,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D245" s="13" t="n">
+      <c r="D245" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E245" t="n">
@@ -8579,7 +8934,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D246" s="13" t="n">
+      <c r="D246" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E246" t="n">
@@ -8603,7 +8958,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D247" s="13" t="n">
+      <c r="D247" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E247" t="n">
@@ -8627,7 +8982,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D248" s="13" t="n">
+      <c r="D248" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E248" t="n">
@@ -8651,7 +9006,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D249" s="13" t="n">
+      <c r="D249" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E249" t="n">
@@ -8675,7 +9030,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D250" s="13" t="n">
+      <c r="D250" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E250" t="n">
@@ -8699,7 +9054,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D251" s="13" t="n">
+      <c r="D251" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E251" t="n">
@@ -8723,7 +9078,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D252" s="13" t="n">
+      <c r="D252" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E252" t="n">
@@ -8747,7 +9102,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D253" s="13" t="n">
+      <c r="D253" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E253" t="n">
@@ -8771,7 +9126,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D254" s="13" t="n">
+      <c r="D254" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E254" t="n">
@@ -8795,7 +9150,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D255" s="13" t="n">
+      <c r="D255" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E255" t="n">
@@ -8819,7 +9174,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D256" s="13" t="n">
+      <c r="D256" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E256" t="n">
@@ -8843,7 +9198,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D257" s="13" t="n">
+      <c r="D257" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E257" t="n">
@@ -8867,7 +9222,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D258" s="13" t="n">
+      <c r="D258" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E258" t="n">
@@ -8891,7 +9246,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D259" s="13" t="n">
+      <c r="D259" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E259" t="n">
@@ -8915,7 +9270,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D260" s="13" t="n">
+      <c r="D260" s="17" t="n">
         <v>46038.33333333334</v>
       </c>
       <c r="E260" t="n">
@@ -8939,7 +9294,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D261" s="13" t="n">
+      <c r="D261" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E261" t="n">
@@ -8963,7 +9318,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D262" s="13" t="n">
+      <c r="D262" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E262" t="n">
@@ -8987,7 +9342,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D263" s="13" t="n">
+      <c r="D263" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E263" t="n">
@@ -9011,7 +9366,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D264" s="13" t="n">
+      <c r="D264" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E264" t="n">
@@ -9035,7 +9390,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D265" s="13" t="n">
+      <c r="D265" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E265" t="n">
@@ -9059,7 +9414,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D266" s="13" t="n">
+      <c r="D266" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E266" t="n">
@@ -9083,7 +9438,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D267" s="13" t="n">
+      <c r="D267" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E267" t="n">
@@ -9107,7 +9462,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D268" s="13" t="n">
+      <c r="D268" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E268" t="n">
@@ -9131,7 +9486,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D269" s="13" t="n">
+      <c r="D269" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E269" t="n">
@@ -9155,7 +9510,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D270" s="13" t="n">
+      <c r="D270" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E270" t="n">
@@ -9179,7 +9534,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D271" s="13" t="n">
+      <c r="D271" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E271" t="n">
@@ -9203,7 +9558,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D272" s="13" t="n">
+      <c r="D272" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E272" t="n">
@@ -9227,7 +9582,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D273" s="13" t="n">
+      <c r="D273" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E273" t="n">
@@ -9251,7 +9606,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D274" s="13" t="n">
+      <c r="D274" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E274" t="n">
@@ -9275,7 +9630,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D275" s="13" t="n">
+      <c r="D275" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E275" t="n">
@@ -9299,7 +9654,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D276" s="13" t="n">
+      <c r="D276" s="17" t="n">
         <v>46039.33333333334</v>
       </c>
       <c r="E276" t="n">
@@ -9323,7 +9678,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D277" s="13" t="n">
+      <c r="D277" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E277" t="n">
@@ -9347,7 +9702,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D278" s="13" t="n">
+      <c r="D278" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E278" t="n">
@@ -9371,7 +9726,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D279" s="13" t="n">
+      <c r="D279" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E279" t="n">
@@ -9395,7 +9750,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D280" s="13" t="n">
+      <c r="D280" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E280" t="n">
@@ -9419,7 +9774,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D281" s="13" t="n">
+      <c r="D281" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E281" t="n">
@@ -9443,7 +9798,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D282" s="13" t="n">
+      <c r="D282" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E282" t="n">
@@ -9467,7 +9822,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D283" s="13" t="n">
+      <c r="D283" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E283" t="n">
@@ -9491,7 +9846,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D284" s="13" t="n">
+      <c r="D284" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E284" t="n">
@@ -9515,7 +9870,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D285" s="13" t="n">
+      <c r="D285" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E285" t="n">
@@ -9539,7 +9894,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D286" s="13" t="n">
+      <c r="D286" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E286" t="n">
@@ -9563,7 +9918,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D287" s="13" t="n">
+      <c r="D287" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E287" t="n">
@@ -9587,7 +9942,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D288" s="13" t="n">
+      <c r="D288" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E288" t="n">
@@ -9611,7 +9966,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D289" s="13" t="n">
+      <c r="D289" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E289" t="n">
@@ -9635,7 +9990,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D290" s="13" t="n">
+      <c r="D290" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E290" t="n">
@@ -9659,7 +10014,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D291" s="13" t="n">
+      <c r="D291" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E291" t="n">
@@ -9683,7 +10038,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D292" s="13" t="n">
+      <c r="D292" s="17" t="n">
         <v>46040.33333333334</v>
       </c>
       <c r="E292" t="n">
@@ -9707,7 +10062,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D293" s="13" t="n">
+      <c r="D293" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E293" t="n">
@@ -9731,7 +10086,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D294" s="13" t="n">
+      <c r="D294" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E294" t="n">
@@ -9755,7 +10110,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D295" s="13" t="n">
+      <c r="D295" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E295" t="n">
@@ -9779,7 +10134,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D296" s="13" t="n">
+      <c r="D296" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E296" t="n">
@@ -9803,7 +10158,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D297" s="13" t="n">
+      <c r="D297" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E297" t="n">
@@ -9827,7 +10182,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D298" s="13" t="n">
+      <c r="D298" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E298" t="n">
@@ -9851,7 +10206,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D299" s="13" t="n">
+      <c r="D299" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E299" t="n">
@@ -9875,7 +10230,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D300" s="13" t="n">
+      <c r="D300" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E300" t="n">
@@ -9899,7 +10254,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D301" s="13" t="n">
+      <c r="D301" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E301" t="n">
@@ -9923,7 +10278,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D302" s="13" t="n">
+      <c r="D302" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E302" t="n">
@@ -9947,7 +10302,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D303" s="13" t="n">
+      <c r="D303" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E303" t="n">
@@ -9971,7 +10326,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D304" s="13" t="n">
+      <c r="D304" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E304" t="n">
@@ -9995,7 +10350,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D305" s="13" t="n">
+      <c r="D305" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E305" t="n">
@@ -10019,7 +10374,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D306" s="13" t="n">
+      <c r="D306" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E306" t="n">
@@ -10043,7 +10398,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D307" s="13" t="n">
+      <c r="D307" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E307" t="n">
@@ -10067,7 +10422,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D308" s="13" t="n">
+      <c r="D308" s="17" t="n">
         <v>46041.33333333334</v>
       </c>
       <c r="E308" t="n">
@@ -10091,7 +10446,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D309" s="13" t="n">
+      <c r="D309" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E309" t="n">
@@ -10115,7 +10470,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D310" s="13" t="n">
+      <c r="D310" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E310" t="n">
@@ -10139,7 +10494,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D311" s="13" t="n">
+      <c r="D311" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E311" t="n">
@@ -10163,7 +10518,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D312" s="13" t="n">
+      <c r="D312" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E312" t="n">
@@ -10187,7 +10542,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D313" s="13" t="n">
+      <c r="D313" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E313" t="n">
@@ -10211,7 +10566,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D314" s="13" t="n">
+      <c r="D314" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E314" t="n">
@@ -10235,7 +10590,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D315" s="13" t="n">
+      <c r="D315" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E315" t="n">
@@ -10259,7 +10614,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D316" s="13" t="n">
+      <c r="D316" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E316" t="n">
@@ -10283,7 +10638,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D317" s="13" t="n">
+      <c r="D317" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E317" t="n">
@@ -10307,7 +10662,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D318" s="13" t="n">
+      <c r="D318" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E318" t="n">
@@ -10331,7 +10686,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D319" s="13" t="n">
+      <c r="D319" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E319" t="n">
@@ -10355,7 +10710,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D320" s="13" t="n">
+      <c r="D320" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E320" t="n">
@@ -10379,7 +10734,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D321" s="13" t="n">
+      <c r="D321" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E321" t="n">
@@ -10403,7 +10758,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D322" s="13" t="n">
+      <c r="D322" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E322" t="n">
@@ -10427,7 +10782,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D323" s="13" t="n">
+      <c r="D323" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E323" t="n">
@@ -10451,7 +10806,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D324" s="13" t="n">
+      <c r="D324" s="17" t="n">
         <v>46042.33333333334</v>
       </c>
       <c r="E324" t="n">
@@ -10475,7 +10830,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D325" s="13" t="n">
+      <c r="D325" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E325" t="n">
@@ -10499,7 +10854,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D326" s="13" t="n">
+      <c r="D326" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E326" t="n">
@@ -10523,7 +10878,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D327" s="13" t="n">
+      <c r="D327" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E327" t="n">
@@ -10547,7 +10902,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D328" s="13" t="n">
+      <c r="D328" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E328" t="n">
@@ -10571,7 +10926,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D329" s="13" t="n">
+      <c r="D329" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E329" t="n">
@@ -10595,7 +10950,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D330" s="13" t="n">
+      <c r="D330" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E330" t="n">
@@ -10619,7 +10974,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D331" s="13" t="n">
+      <c r="D331" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E331" t="n">
@@ -10643,7 +10998,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D332" s="13" t="n">
+      <c r="D332" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E332" t="n">
@@ -10667,7 +11022,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D333" s="13" t="n">
+      <c r="D333" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E333" t="n">
@@ -10691,7 +11046,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D334" s="13" t="n">
+      <c r="D334" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E334" t="n">
@@ -10715,7 +11070,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D335" s="13" t="n">
+      <c r="D335" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E335" t="n">
@@ -10739,7 +11094,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D336" s="13" t="n">
+      <c r="D336" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E336" t="n">
@@ -10763,7 +11118,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D337" s="13" t="n">
+      <c r="D337" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E337" t="n">
@@ -10787,7 +11142,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D338" s="13" t="n">
+      <c r="D338" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E338" t="n">
@@ -10811,7 +11166,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D339" s="13" t="n">
+      <c r="D339" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E339" t="n">
@@ -10835,7 +11190,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D340" s="13" t="n">
+      <c r="D340" s="17" t="n">
         <v>46043.33333333334</v>
       </c>
       <c r="E340" t="n">
@@ -10859,7 +11214,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D341" s="13" t="n">
+      <c r="D341" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E341" t="n">
@@ -10883,7 +11238,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D342" s="13" t="n">
+      <c r="D342" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E342" t="n">
@@ -10907,7 +11262,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D343" s="13" t="n">
+      <c r="D343" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E343" t="n">
@@ -10931,7 +11286,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D344" s="13" t="n">
+      <c r="D344" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E344" t="n">
@@ -10955,7 +11310,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D345" s="13" t="n">
+      <c r="D345" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E345" t="n">
@@ -10979,7 +11334,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D346" s="13" t="n">
+      <c r="D346" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E346" t="n">
@@ -11003,7 +11358,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D347" s="13" t="n">
+      <c r="D347" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E347" t="n">
@@ -11027,7 +11382,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D348" s="13" t="n">
+      <c r="D348" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E348" t="n">
@@ -11051,7 +11406,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D349" s="13" t="n">
+      <c r="D349" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E349" t="n">
@@ -11075,7 +11430,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D350" s="13" t="n">
+      <c r="D350" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E350" t="n">
@@ -11099,7 +11454,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D351" s="13" t="n">
+      <c r="D351" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E351" t="n">
@@ -11123,7 +11478,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D352" s="13" t="n">
+      <c r="D352" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E352" t="n">
@@ -11147,7 +11502,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D353" s="13" t="n">
+      <c r="D353" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E353" t="n">
@@ -11171,7 +11526,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D354" s="13" t="n">
+      <c r="D354" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E354" t="n">
@@ -11195,7 +11550,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D355" s="13" t="n">
+      <c r="D355" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E355" t="n">
@@ -11219,7 +11574,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D356" s="13" t="n">
+      <c r="D356" s="17" t="n">
         <v>46044.33333333334</v>
       </c>
       <c r="E356" t="n">
@@ -11243,7 +11598,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D357" s="13" t="n">
+      <c r="D357" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E357" t="n">
@@ -11267,7 +11622,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D358" s="13" t="n">
+      <c r="D358" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E358" t="n">
@@ -11291,7 +11646,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D359" s="13" t="n">
+      <c r="D359" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E359" t="n">
@@ -11315,7 +11670,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D360" s="13" t="n">
+      <c r="D360" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E360" t="n">
@@ -11339,7 +11694,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D361" s="13" t="n">
+      <c r="D361" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E361" t="n">
@@ -11363,7 +11718,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D362" s="13" t="n">
+      <c r="D362" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E362" t="n">
@@ -11387,7 +11742,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D363" s="13" t="n">
+      <c r="D363" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E363" t="n">
@@ -11411,7 +11766,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D364" s="13" t="n">
+      <c r="D364" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E364" t="n">
@@ -11435,7 +11790,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D365" s="13" t="n">
+      <c r="D365" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E365" t="n">
@@ -11459,7 +11814,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D366" s="13" t="n">
+      <c r="D366" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E366" t="n">
@@ -11483,7 +11838,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D367" s="13" t="n">
+      <c r="D367" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E367" t="n">
@@ -11507,7 +11862,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D368" s="13" t="n">
+      <c r="D368" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E368" t="n">
@@ -11531,7 +11886,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D369" s="13" t="n">
+      <c r="D369" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E369" t="n">
@@ -11555,7 +11910,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D370" s="13" t="n">
+      <c r="D370" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E370" t="n">
@@ -11579,7 +11934,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D371" s="13" t="n">
+      <c r="D371" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E371" t="n">
@@ -11603,7 +11958,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D372" s="13" t="n">
+      <c r="D372" s="17" t="n">
         <v>46045.33333333334</v>
       </c>
       <c r="E372" t="n">
@@ -11627,7 +11982,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D373" s="13" t="n">
+      <c r="D373" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E373" t="n">
@@ -11651,7 +12006,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D374" s="13" t="n">
+      <c r="D374" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E374" t="n">
@@ -11675,7 +12030,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D375" s="13" t="n">
+      <c r="D375" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E375" t="n">
@@ -11699,7 +12054,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D376" s="13" t="n">
+      <c r="D376" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E376" t="n">
@@ -11723,7 +12078,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D377" s="13" t="n">
+      <c r="D377" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E377" t="n">
@@ -11747,7 +12102,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D378" s="13" t="n">
+      <c r="D378" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E378" t="n">
@@ -11771,7 +12126,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D379" s="13" t="n">
+      <c r="D379" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E379" t="n">
@@ -11795,7 +12150,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D380" s="13" t="n">
+      <c r="D380" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E380" t="n">
@@ -11819,7 +12174,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D381" s="13" t="n">
+      <c r="D381" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E381" t="n">
@@ -11843,7 +12198,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D382" s="13" t="n">
+      <c r="D382" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E382" t="n">
@@ -11867,7 +12222,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D383" s="13" t="n">
+      <c r="D383" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E383" t="n">
@@ -11891,7 +12246,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D384" s="13" t="n">
+      <c r="D384" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E384" t="n">
@@ -11915,7 +12270,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D385" s="13" t="n">
+      <c r="D385" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E385" t="n">
@@ -11939,7 +12294,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D386" s="13" t="n">
+      <c r="D386" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E386" t="n">
@@ -11963,7 +12318,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D387" s="13" t="n">
+      <c r="D387" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E387" t="n">
@@ -11987,7 +12342,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D388" s="13" t="n">
+      <c r="D388" s="17" t="n">
         <v>46046.33333333334</v>
       </c>
       <c r="E388" t="n">
@@ -12011,7 +12366,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D389" s="13" t="n">
+      <c r="D389" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E389" t="n">
@@ -12035,7 +12390,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D390" s="13" t="n">
+      <c r="D390" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E390" t="n">
@@ -12059,7 +12414,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D391" s="13" t="n">
+      <c r="D391" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E391" t="n">
@@ -12083,7 +12438,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D392" s="13" t="n">
+      <c r="D392" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E392" t="n">
@@ -12107,7 +12462,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D393" s="13" t="n">
+      <c r="D393" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E393" t="n">
@@ -12131,7 +12486,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D394" s="13" t="n">
+      <c r="D394" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E394" t="n">
@@ -12155,7 +12510,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D395" s="13" t="n">
+      <c r="D395" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E395" t="n">
@@ -12179,7 +12534,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D396" s="13" t="n">
+      <c r="D396" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E396" t="n">
@@ -12203,7 +12558,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D397" s="13" t="n">
+      <c r="D397" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E397" t="n">
@@ -12227,7 +12582,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D398" s="13" t="n">
+      <c r="D398" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E398" t="n">
@@ -12251,7 +12606,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D399" s="13" t="n">
+      <c r="D399" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E399" t="n">
@@ -12275,7 +12630,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D400" s="13" t="n">
+      <c r="D400" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E400" t="n">
@@ -12299,7 +12654,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D401" s="13" t="n">
+      <c r="D401" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E401" t="n">
@@ -12323,7 +12678,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D402" s="13" t="n">
+      <c r="D402" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E402" t="n">
@@ -12347,7 +12702,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D403" s="13" t="n">
+      <c r="D403" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E403" t="n">
@@ -12371,7 +12726,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D404" s="13" t="n">
+      <c r="D404" s="17" t="n">
         <v>46047.33333333334</v>
       </c>
       <c r="E404" t="n">
@@ -12395,7 +12750,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D405" s="13" t="n">
+      <c r="D405" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E405" t="n">
@@ -12419,7 +12774,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D406" s="13" t="n">
+      <c r="D406" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E406" t="n">
@@ -12443,7 +12798,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D407" s="13" t="n">
+      <c r="D407" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E407" t="n">
@@ -12467,7 +12822,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D408" s="13" t="n">
+      <c r="D408" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E408" t="n">
@@ -12491,7 +12846,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D409" s="13" t="n">
+      <c r="D409" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E409" t="n">
@@ -12515,7 +12870,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D410" s="13" t="n">
+      <c r="D410" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E410" t="n">
@@ -12539,7 +12894,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D411" s="13" t="n">
+      <c r="D411" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E411" t="n">
@@ -12563,7 +12918,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D412" s="13" t="n">
+      <c r="D412" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E412" t="n">
@@ -12587,7 +12942,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D413" s="13" t="n">
+      <c r="D413" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E413" t="n">
@@ -12611,7 +12966,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D414" s="13" t="n">
+      <c r="D414" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E414" t="n">
@@ -12635,7 +12990,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D415" s="13" t="n">
+      <c r="D415" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E415" t="n">
@@ -12659,7 +13014,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D416" s="13" t="n">
+      <c r="D416" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E416" t="n">
@@ -12683,7 +13038,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D417" s="13" t="n">
+      <c r="D417" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E417" t="n">
@@ -12707,7 +13062,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D418" s="13" t="n">
+      <c r="D418" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E418" t="n">
@@ -12731,7 +13086,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D419" s="13" t="n">
+      <c r="D419" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E419" t="n">
@@ -12755,7 +13110,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D420" s="13" t="n">
+      <c r="D420" s="17" t="n">
         <v>46048.33333333334</v>
       </c>
       <c r="E420" t="n">
@@ -12779,7 +13134,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D421" s="13" t="n">
+      <c r="D421" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E421" t="n">
@@ -12803,7 +13158,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D422" s="13" t="n">
+      <c r="D422" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E422" t="n">
@@ -12827,7 +13182,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D423" s="13" t="n">
+      <c r="D423" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E423" t="n">
@@ -12851,7 +13206,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D424" s="13" t="n">
+      <c r="D424" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E424" t="n">
@@ -12875,7 +13230,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D425" s="13" t="n">
+      <c r="D425" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E425" t="n">
@@ -12899,7 +13254,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D426" s="13" t="n">
+      <c r="D426" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E426" t="n">
@@ -12923,7 +13278,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D427" s="13" t="n">
+      <c r="D427" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E427" t="n">
@@ -12947,7 +13302,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D428" s="13" t="n">
+      <c r="D428" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E428" t="n">
@@ -12971,7 +13326,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D429" s="13" t="n">
+      <c r="D429" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E429" t="n">
@@ -12995,7 +13350,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D430" s="13" t="n">
+      <c r="D430" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E430" t="n">
@@ -13019,7 +13374,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D431" s="13" t="n">
+      <c r="D431" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E431" t="n">
@@ -13043,7 +13398,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D432" s="13" t="n">
+      <c r="D432" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E432" t="n">
@@ -13067,7 +13422,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D433" s="13" t="n">
+      <c r="D433" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E433" t="n">
@@ -13091,7 +13446,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D434" s="13" t="n">
+      <c r="D434" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E434" t="n">
@@ -13115,7 +13470,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D435" s="13" t="n">
+      <c r="D435" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E435" t="n">
@@ -13139,7 +13494,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D436" s="13" t="n">
+      <c r="D436" s="17" t="n">
         <v>46049.33333333334</v>
       </c>
       <c r="E436" t="n">
@@ -13163,7 +13518,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D437" s="13" t="n">
+      <c r="D437" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E437" t="n">
@@ -13187,7 +13542,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D438" s="13" t="n">
+      <c r="D438" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E438" t="n">
@@ -13211,7 +13566,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D439" s="13" t="n">
+      <c r="D439" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E439" t="n">
@@ -13235,7 +13590,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D440" s="13" t="n">
+      <c r="D440" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E440" t="n">
@@ -13259,7 +13614,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D441" s="13" t="n">
+      <c r="D441" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E441" t="n">
@@ -13283,7 +13638,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D442" s="13" t="n">
+      <c r="D442" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E442" t="n">
@@ -13307,7 +13662,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D443" s="13" t="n">
+      <c r="D443" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E443" t="n">
@@ -13331,7 +13686,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D444" s="13" t="n">
+      <c r="D444" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E444" t="n">
@@ -13355,7 +13710,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D445" s="13" t="n">
+      <c r="D445" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E445" t="n">
@@ -13379,7 +13734,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D446" s="13" t="n">
+      <c r="D446" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E446" t="n">
@@ -13403,7 +13758,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D447" s="13" t="n">
+      <c r="D447" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E447" t="n">
@@ -13427,7 +13782,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D448" s="13" t="n">
+      <c r="D448" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E448" t="n">
@@ -13451,7 +13806,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D449" s="13" t="n">
+      <c r="D449" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E449" t="n">
@@ -13475,7 +13830,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D450" s="13" t="n">
+      <c r="D450" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E450" t="n">
@@ -13499,7 +13854,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D451" s="13" t="n">
+      <c r="D451" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E451" t="n">
@@ -13523,7 +13878,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D452" s="13" t="n">
+      <c r="D452" s="17" t="n">
         <v>46050.33333333334</v>
       </c>
       <c r="E452" t="n">
@@ -13547,7 +13902,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D453" s="13" t="n">
+      <c r="D453" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E453" t="n">
@@ -13571,7 +13926,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D454" s="13" t="n">
+      <c r="D454" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E454" t="n">
@@ -13595,7 +13950,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D455" s="13" t="n">
+      <c r="D455" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E455" t="n">
@@ -13619,7 +13974,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D456" s="13" t="n">
+      <c r="D456" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E456" t="n">
@@ -13643,7 +13998,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D457" s="13" t="n">
+      <c r="D457" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E457" t="n">
@@ -13667,7 +14022,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D458" s="13" t="n">
+      <c r="D458" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E458" t="n">
@@ -13691,7 +14046,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D459" s="13" t="n">
+      <c r="D459" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E459" t="n">
@@ -13715,7 +14070,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D460" s="13" t="n">
+      <c r="D460" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E460" t="n">
@@ -13739,7 +14094,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D461" s="13" t="n">
+      <c r="D461" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E461" t="n">
@@ -13763,7 +14118,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D462" s="13" t="n">
+      <c r="D462" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E462" t="n">
@@ -13787,7 +14142,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D463" s="13" t="n">
+      <c r="D463" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E463" t="n">
@@ -13811,7 +14166,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D464" s="13" t="n">
+      <c r="D464" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E464" t="n">
@@ -13835,7 +14190,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D465" s="13" t="n">
+      <c r="D465" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E465" t="n">
@@ -13859,7 +14214,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D466" s="13" t="n">
+      <c r="D466" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E466" t="n">
@@ -13883,7 +14238,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D467" s="13" t="n">
+      <c r="D467" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E467" t="n">
@@ -13907,7 +14262,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D468" s="13" t="n">
+      <c r="D468" s="17" t="n">
         <v>46051.33333333334</v>
       </c>
       <c r="E468" t="n">
@@ -13931,7 +14286,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D469" s="13" t="n">
+      <c r="D469" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E469" t="n">
@@ -13955,7 +14310,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D470" s="13" t="n">
+      <c r="D470" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E470" t="n">
@@ -13979,7 +14334,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D471" s="13" t="n">
+      <c r="D471" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E471" t="n">
@@ -14003,7 +14358,7 @@
           <t>Line-A</t>
         </is>
       </c>
-      <c r="D472" s="13" t="n">
+      <c r="D472" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E472" t="n">
@@ -14027,7 +14382,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D473" s="13" t="n">
+      <c r="D473" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E473" t="n">
@@ -14051,7 +14406,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D474" s="13" t="n">
+      <c r="D474" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E474" t="n">
@@ -14075,7 +14430,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D475" s="13" t="n">
+      <c r="D475" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E475" t="n">
@@ -14099,7 +14454,7 @@
           <t>Line-B</t>
         </is>
       </c>
-      <c r="D476" s="13" t="n">
+      <c r="D476" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E476" t="n">
@@ -14123,7 +14478,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D477" s="13" t="n">
+      <c r="D477" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E477" t="n">
@@ -14147,7 +14502,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D478" s="13" t="n">
+      <c r="D478" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E478" t="n">
@@ -14171,7 +14526,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D479" s="13" t="n">
+      <c r="D479" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E479" t="n">
@@ -14195,7 +14550,7 @@
           <t>Line-C</t>
         </is>
       </c>
-      <c r="D480" s="13" t="n">
+      <c r="D480" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E480" t="n">
@@ -14219,7 +14574,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D481" s="13" t="n">
+      <c r="D481" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E481" t="n">
@@ -14243,7 +14598,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D482" s="13" t="n">
+      <c r="D482" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E482" t="n">
@@ -14267,7 +14622,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D483" s="13" t="n">
+      <c r="D483" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E483" t="n">
@@ -14291,7 +14646,7 @@
           <t>Line-D</t>
         </is>
       </c>
-      <c r="D484" s="13" t="n">
+      <c r="D484" s="17" t="n">
         <v>46052.33333333334</v>
       </c>
       <c r="E484" t="n">
@@ -14352,42 +14707,42 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Generated At</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Machines</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Report Sheet</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>PDF File</t>
         </is>
@@ -14409,7 +14764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J12"/>
+  <dimension ref="B1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -14421,7 +14776,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -14432,163 +14787,151 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ONE-TIME SETUP</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Press Alt+F11 to open the VBA editor.</t>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Alt+F11 → File → Import File… → pick vba/MachineMonitor.bas. Save As Macro-Enabled Workbook (*.xlsm). Then Alt+F8 → SetupWorkbook → Run.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="9" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>File → Import File… → select vba/MachineMonitor.bas.</t>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CONFIGURE</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Config sheet holds up to 16 machines. Or add machines live from the Dashboard using the ADD MACHINE panel.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="9" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Close the editor. File → Save As → choose 'Excel Macro-Enabled Workbook (*.xlsm)'.</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>IMPORT DATA</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard → IMPORT CSV. CSV columns: machine_id, tag, timestamp, metric1, metric2, metric3.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Run macro 'SetupWorkbook' once (Alt+F8 → SetupWorkbook → Run). This adds the buttons.</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Set Start / End dates + Tag. Click REFRESH DASHBOARD to populate the machine picker.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>CONFIGURE</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Open the Config sheet. Edit machine names, tags, and metric names for up to 16 rows.</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>PICK MACHINES</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>In 'MACHINES TO COMPARE', untick any machine you want to exclude, then REFRESH again.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>IMPORT DATA</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>On Dashboard, click IMPORT CSV. Pick a CSV with columns: machine_id, tag, timestamp, metric1, metric2, metric3.</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>GENERATE REPORT creates a frozen snapshot sheet + a PDF next to the workbook.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>FILTER</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Pick Start Date, End Date, and Tag Group. Click REFRESH DASHBOARD.</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SHORTCUTS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Ctrl+Shift+I Import   |   Ctrl+Shift+R Refresh   |   Ctrl+Shift+G Report.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>REPORT</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Click GENERATE REPORT → creates a new sheet + PDF alongside the workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>SHORTCUTS</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+Shift+I  Import   |   Ctrl+Shift+R  Refresh   |   Ctrl+Shift+G  Generate Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>LIVE UPDATES</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>The macro AutoRefresh() is scheduled every 60s once you enable it via 'ToggleLive'. Turn on later when the data feed is ready.</t>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Run ToggleLive to auto-refresh every 60 sec (for when you wire in a live feed later).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="B1:H1"/>
     <mergeCell ref="D3:J3"/>
     <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D12:J12"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D6:J6"/>
+    <mergeCell ref="B1:J1"/>
     <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
     <mergeCell ref="D5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
